--- a/dataset/bd_principal.xlsx
+++ b/dataset/bd_principal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2597,48 +2597,48 @@
         <v>46175</v>
       </c>
       <c r="B44" t="n">
-        <v>300242506</v>
+        <v>300258637</v>
       </c>
       <c r="C44" t="n">
-        <v>16378652</v>
+        <v>16152107</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>JOSENI MARIA DE MEDEIROS</t>
+          <t>M K INDUSTRIA TEXTIL LTDA</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ETIQUETA</t>
+          <t>REVEL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SEM ARREMATE</t>
+          <t>ESGARÇANDO</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1248</v>
+        <v>798</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0008012820512820513</v>
+        <v>0.08897243107769423</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ETIQUETASEM ARREMATE</t>
+          <t>REVELESGARÇANDO</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.33</v>
+        <v>2.84</v>
       </c>
       <c r="L44" t="n">
-        <v>0.33</v>
+        <v>201.64</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3861</v>
+        <v>235.9188</v>
       </c>
       <c r="N44" t="inlineStr"/>
     </row>
@@ -2647,22 +2647,22 @@
         <v>46175</v>
       </c>
       <c r="B45" t="n">
-        <v>300242506</v>
+        <v>300258637</v>
       </c>
       <c r="C45" t="n">
-        <v>16378652</v>
+        <v>16152107</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>JOSENI MARIA DE MEDEIROS</t>
+          <t>M K INDUSTRIA TEXTIL LTDA</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CINTO DO SHORT</t>
+          <t>CÓS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2671,24 +2671,24 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1248</v>
+        <v>798</v>
       </c>
       <c r="I45" t="n">
-        <v>0.005608974358974359</v>
+        <v>0.04636591478696742</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>CINTO DO SHORTPONTO ESTOURADO</t>
+          <t>CÓSPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="L45" t="n">
-        <v>6.16</v>
+        <v>11.47</v>
       </c>
       <c r="M45" t="n">
-        <v>7.207199999999999</v>
+        <v>13.4199</v>
       </c>
       <c r="N45" t="inlineStr"/>
     </row>
@@ -2697,48 +2697,48 @@
         <v>46175</v>
       </c>
       <c r="B46" t="n">
-        <v>300242506</v>
+        <v>300258637</v>
       </c>
       <c r="C46" t="n">
-        <v>16378652</v>
+        <v>16152107</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JOSENI MARIA DE MEDEIROS</t>
+          <t>M K INDUSTRIA TEXTIL LTDA</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CÓS</t>
+          <t>ETIQUETA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PONTO ESTOURADO</t>
+          <t>SEM ARREMATE</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1248</v>
+        <v>798</v>
       </c>
       <c r="I46" t="n">
-        <v>0.001602564102564103</v>
+        <v>0.008771929824561403</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>CÓSPONTO ESTOURADO</t>
+          <t>ETIQUETASEM ARREMATE</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="L46" t="n">
-        <v>0.62</v>
+        <v>2.31</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7253999999999999</v>
+        <v>2.7027</v>
       </c>
       <c r="N46" t="inlineStr"/>
     </row>
@@ -2747,48 +2747,48 @@
         <v>46175</v>
       </c>
       <c r="B47" t="n">
-        <v>300259106</v>
+        <v>300242506</v>
       </c>
       <c r="C47" t="n">
-        <v>16292740</v>
+        <v>16378652</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>J M CONFECCOES &amp; CIA LTDA MATRIZ</t>
+          <t>JOSENI MARIA DE MEDEIROS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CÓS</t>
+          <t>ETIQUETA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PONTO ESTOURADO</t>
+          <t>SEM ARREMATE</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1104</v>
+        <v>1248</v>
       </c>
       <c r="I47" t="n">
-        <v>0.009963768115942028</v>
+        <v>0.0008012820512820513</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>CÓSPONTO ESTOURADO</t>
+          <t>ETIQUETASEM ARREMATE</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="L47" t="n">
-        <v>3.41</v>
+        <v>0.33</v>
       </c>
       <c r="M47" t="n">
-        <v>3.9897</v>
+        <v>0.3861</v>
       </c>
       <c r="N47" t="inlineStr"/>
     </row>
@@ -2797,48 +2797,48 @@
         <v>46175</v>
       </c>
       <c r="B48" t="n">
-        <v>300259106</v>
+        <v>300242506</v>
       </c>
       <c r="C48" t="n">
-        <v>16292740</v>
+        <v>16378652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>J M CONFECCOES &amp; CIA LTDA MATRIZ</t>
+          <t>JOSENI MARIA DE MEDEIROS</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ETIQUETA</t>
+          <t>CINTO DO SHORT</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SEM ARREMATE</t>
+          <t>PONTO ESTOURADO</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1104</v>
+        <v>1248</v>
       </c>
       <c r="I48" t="n">
-        <v>0.002717391304347826</v>
+        <v>0.005608974358974359</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>ETIQUETASEM ARREMATE</t>
+          <t>CINTO DO SHORTPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.33</v>
+        <v>0.88</v>
       </c>
       <c r="L48" t="n">
-        <v>0.99</v>
+        <v>6.16</v>
       </c>
       <c r="M48" t="n">
-        <v>1.1583</v>
+        <v>7.207199999999999</v>
       </c>
       <c r="N48" t="inlineStr"/>
     </row>
@@ -2847,14 +2847,14 @@
         <v>46175</v>
       </c>
       <c r="B49" t="n">
-        <v>300259106</v>
+        <v>300242506</v>
       </c>
       <c r="C49" t="n">
-        <v>16292740</v>
+        <v>16378652</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>J M CONFECCOES &amp; CIA LTDA MATRIZ</t>
+          <t>JOSENI MARIA DE MEDEIROS</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BOLSO TRASEIRO</t>
+          <t>CÓS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2871,24 +2871,24 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1104</v>
+        <v>1248</v>
       </c>
       <c r="I49" t="n">
-        <v>0.001811594202898551</v>
+        <v>0.001602564102564103</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>BOLSO TRASEIROPONTO ESTOURADO</t>
+          <t>CÓSPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1.09</v>
+        <v>0.31</v>
       </c>
       <c r="L49" t="n">
-        <v>2.18</v>
+        <v>0.62</v>
       </c>
       <c r="M49" t="n">
-        <v>2.5506</v>
+        <v>0.7253999999999999</v>
       </c>
       <c r="N49" t="inlineStr"/>
     </row>
@@ -2897,22 +2897,22 @@
         <v>46175</v>
       </c>
       <c r="B50" t="n">
-        <v>300248793</v>
+        <v>300259106</v>
       </c>
       <c r="C50" t="n">
-        <v>16324650</v>
+        <v>16292740</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DANTAS E PAULINO CONFECCOES LTDA</t>
+          <t>J M CONFECCOES &amp; CIA LTDA MATRIZ</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BARRA</t>
+          <t>CÓS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2921,24 +2921,24 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>504</v>
+        <v>1104</v>
       </c>
       <c r="I50" t="n">
-        <v>0.003968253968253968</v>
+        <v>0.009963768115942028</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>BARRAPONTO ESTOURADO</t>
+          <t>CÓSPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.8</v>
+        <v>0.31</v>
       </c>
       <c r="L50" t="n">
-        <v>1.6</v>
+        <v>3.41</v>
       </c>
       <c r="M50" t="n">
-        <v>1.872</v>
+        <v>3.9897</v>
       </c>
       <c r="N50" t="inlineStr"/>
     </row>
@@ -2947,48 +2947,48 @@
         <v>46175</v>
       </c>
       <c r="B51" t="n">
-        <v>300259165</v>
+        <v>300259106</v>
       </c>
       <c r="C51" t="n">
-        <v>16466063</v>
+        <v>16292740</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CONFECÇÕES J.S.LTDA</t>
+          <t>J M CONFECCOES &amp; CIA LTDA MATRIZ</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CÓS</t>
+          <t>ETIQUETA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PONTO ESTOURADO</t>
+          <t>SEM ARREMATE</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>831</v>
+        <v>1104</v>
       </c>
       <c r="I51" t="n">
-        <v>0.001203369434416366</v>
+        <v>0.002717391304347826</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>CÓSPONTO ESTOURADO</t>
+          <t>ETIQUETASEM ARREMATE</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="L51" t="n">
-        <v>0.31</v>
+        <v>0.99</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3627</v>
+        <v>1.1583</v>
       </c>
       <c r="N51" t="inlineStr"/>
     </row>
@@ -2997,48 +2997,48 @@
         <v>46175</v>
       </c>
       <c r="B52" t="n">
-        <v>300259165</v>
+        <v>300259106</v>
       </c>
       <c r="C52" t="n">
-        <v>16466063</v>
+        <v>16292740</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CONFECÇÕES J.S.LTDA</t>
+          <t>J M CONFECCOES &amp; CIA LTDA MATRIZ</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ETIQUETA</t>
+          <t>BOLSO TRASEIRO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SEM ARREMATE</t>
+          <t>PONTO ESTOURADO</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>831</v>
+        <v>1104</v>
       </c>
       <c r="I52" t="n">
-        <v>0.001203369434416366</v>
+        <v>0.001811594202898551</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>ETIQUETASEM ARREMATE</t>
+          <t>BOLSO TRASEIROPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.33</v>
+        <v>1.09</v>
       </c>
       <c r="L52" t="n">
-        <v>0.33</v>
+        <v>2.18</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3861</v>
+        <v>2.5506</v>
       </c>
       <c r="N52" t="inlineStr"/>
     </row>
@@ -3047,48 +3047,48 @@
         <v>46175</v>
       </c>
       <c r="B53" t="n">
-        <v>300248793</v>
+        <v>300258637</v>
       </c>
       <c r="C53" t="n">
-        <v>16324650</v>
+        <v>16152107</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DANTAS E PAULINO CONFECCOES LTDA</t>
+          <t>M K INDUSTRIA TEXTIL LTDA</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BARRA</t>
+          <t>CÓS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PONTO ESTOURADO</t>
+          <t>ESGARÇANDO</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>504</v>
+        <v>798</v>
       </c>
       <c r="I53" t="n">
-        <v>0.003968253968253968</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>BARRAPONTO ESTOURADO</t>
+          <t>CÓSESGARÇANDO</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.8</v>
+        <v>11.13</v>
       </c>
       <c r="L53" t="n">
-        <v>1.6</v>
+        <v>211.47</v>
       </c>
       <c r="M53" t="n">
-        <v>1.872</v>
+        <v>247.4199</v>
       </c>
       <c r="N53" t="inlineStr"/>
     </row>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>504</v>
       </c>
       <c r="I54" t="n">
-        <v>0.001984126984126984</v>
+        <v>0.003968253968253968</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
         <v>0.8</v>
       </c>
       <c r="L54" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="M54" t="n">
-        <v>0.9359999999999999</v>
+        <v>1.872</v>
       </c>
       <c r="N54" t="inlineStr"/>
     </row>
@@ -3147,14 +3147,14 @@
         <v>46175</v>
       </c>
       <c r="B55" t="n">
-        <v>300248793</v>
+        <v>300259165</v>
       </c>
       <c r="C55" t="n">
-        <v>16324650</v>
+        <v>16466063</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DANTAS E PAULINO CONFECCOES LTDA</t>
+          <t>CONFECÇÕES J.S.LTDA</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BOLSO RELOGIO</t>
+          <t>CÓS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3171,24 +3171,24 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>504</v>
+        <v>831</v>
       </c>
       <c r="I55" t="n">
-        <v>0.001984126984126984</v>
+        <v>0.001203369434416366</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>BOLSO RELOGIOPONTO ESTOURADO</t>
+          <t>CÓSPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.8</v>
+        <v>0.31</v>
       </c>
       <c r="L55" t="n">
-        <v>0.8</v>
+        <v>0.31</v>
       </c>
       <c r="M55" t="n">
-        <v>0.9359999999999999</v>
+        <v>0.3627</v>
       </c>
       <c r="N55" t="inlineStr"/>
     </row>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>831</v>
       </c>
       <c r="I56" t="n">
-        <v>0.01083032490974729</v>
+        <v>0.001203369434416366</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
         <v>0.33</v>
       </c>
       <c r="L56" t="n">
-        <v>2.97</v>
+        <v>0.33</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4749</v>
+        <v>0.3861</v>
       </c>
       <c r="N56" t="inlineStr"/>
     </row>
@@ -3247,22 +3247,22 @@
         <v>46175</v>
       </c>
       <c r="B57" t="n">
-        <v>300259165</v>
+        <v>300248793</v>
       </c>
       <c r="C57" t="n">
-        <v>16466063</v>
+        <v>16324650</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CONFECÇÕES J.S.LTDA</t>
+          <t>DANTAS E PAULINO CONFECCOES LTDA</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CÓS</t>
+          <t>BARRA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3271,24 +3271,24 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>831</v>
+        <v>504</v>
       </c>
       <c r="I57" t="n">
-        <v>0.001203369434416366</v>
+        <v>0.003968253968253968</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>CÓSPONTO ESTOURADO</t>
+          <t>BARRAPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.31</v>
+        <v>0.8</v>
       </c>
       <c r="L57" t="n">
-        <v>0.31</v>
+        <v>1.6</v>
       </c>
       <c r="M57" t="n">
-        <v>0.3627</v>
+        <v>1.872</v>
       </c>
       <c r="N57" t="inlineStr"/>
     </row>
@@ -3297,22 +3297,22 @@
         <v>46175</v>
       </c>
       <c r="B58" t="n">
-        <v>300259106</v>
+        <v>300248793</v>
       </c>
       <c r="C58" t="n">
-        <v>16292740</v>
+        <v>16324650</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>J M CONFECCOES &amp; CIA LTDA MATRIZ</t>
+          <t>DANTAS E PAULINO CONFECCOES LTDA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CÓS</t>
+          <t>BARRA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3321,24 +3321,24 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1104</v>
+        <v>504</v>
       </c>
       <c r="I58" t="n">
-        <v>0.01358695652173913</v>
+        <v>0.001984126984126984</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>CÓSPONTO ESTOURADO</t>
+          <t>BARRAPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.31</v>
+        <v>0.8</v>
       </c>
       <c r="L58" t="n">
-        <v>4.65</v>
+        <v>0.8</v>
       </c>
       <c r="M58" t="n">
-        <v>5.4405</v>
+        <v>0.9359999999999999</v>
       </c>
       <c r="N58" t="inlineStr"/>
     </row>
@@ -3347,22 +3347,22 @@
         <v>46175</v>
       </c>
       <c r="B59" t="n">
-        <v>300242506</v>
+        <v>300248793</v>
       </c>
       <c r="C59" t="n">
-        <v>16378652</v>
+        <v>16324650</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>JOSENI MARIA DE MEDEIROS</t>
+          <t>DANTAS E PAULINO CONFECCOES LTDA</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CINTO DO SHORT</t>
+          <t>BOLSO RELOGIO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3371,24 +3371,24 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1248</v>
+        <v>504</v>
       </c>
       <c r="I59" t="n">
-        <v>0.01602564102564102</v>
+        <v>0.001984126984126984</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>CINTO DO SHORTPONTO ESTOURADO</t>
+          <t>BOLSO RELOGIOPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="L59" t="n">
-        <v>17.6</v>
+        <v>0.8</v>
       </c>
       <c r="M59" t="n">
-        <v>20.592</v>
+        <v>0.9359999999999999</v>
       </c>
       <c r="N59" t="inlineStr"/>
     </row>
@@ -3397,18 +3397,18 @@
         <v>46175</v>
       </c>
       <c r="B60" t="n">
-        <v>300234852</v>
+        <v>300259165</v>
       </c>
       <c r="C60" t="n">
-        <v>15764494</v>
+        <v>16466063</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TENDENCIA CONFECCOES LTDA - ME</t>
+          <t>CONFECÇÕES J.S.LTDA</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1368</v>
+        <v>831</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0007309941520467836</v>
+        <v>0.01083032490974729</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3435,10 +3435,10 @@
         <v>0.33</v>
       </c>
       <c r="L60" t="n">
-        <v>0.33</v>
+        <v>2.97</v>
       </c>
       <c r="M60" t="n">
-        <v>0.3861</v>
+        <v>3.4749</v>
       </c>
       <c r="N60" t="inlineStr"/>
     </row>
@@ -3447,14 +3447,14 @@
         <v>46175</v>
       </c>
       <c r="B61" t="n">
-        <v>300234852</v>
+        <v>300259165</v>
       </c>
       <c r="C61" t="n">
-        <v>15764494</v>
+        <v>16466063</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TENDENCIA CONFECCOES LTDA - ME</t>
+          <t>CONFECÇÕES J.S.LTDA</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PASSANTE</t>
+          <t>CÓS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3471,24 +3471,24 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1368</v>
+        <v>831</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0007309941520467836</v>
+        <v>0.001203369434416366</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>PASSANTEPONTO ESTOURADO</t>
+          <t>CÓSPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="L61" t="n">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.3627</v>
       </c>
       <c r="N61" t="inlineStr"/>
     </row>
@@ -3497,18 +3497,18 @@
         <v>46175</v>
       </c>
       <c r="B62" t="n">
-        <v>300253749</v>
+        <v>300259106</v>
       </c>
       <c r="C62" t="n">
-        <v>16450302</v>
+        <v>16292740</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FACCAO ELLO LTDA - ME</t>
+          <t>J M CONFECCOES &amp; CIA LTDA MATRIZ</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1232</v>
+        <v>1104</v>
       </c>
       <c r="I62" t="n">
-        <v>0.008928571428571428</v>
+        <v>0.01358695652173913</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3535,10 +3535,10 @@
         <v>0.31</v>
       </c>
       <c r="L62" t="n">
-        <v>3.41</v>
+        <v>4.65</v>
       </c>
       <c r="M62" t="n">
-        <v>3.9897</v>
+        <v>5.4405</v>
       </c>
       <c r="N62" t="inlineStr"/>
     </row>
@@ -3547,22 +3547,22 @@
         <v>46175</v>
       </c>
       <c r="B63" t="n">
-        <v>300259131</v>
+        <v>300242506</v>
       </c>
       <c r="C63" t="n">
-        <v>16482204</v>
+        <v>16378652</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>POEST INDUSTRIA COMERCIO VESTUARIO LTDA</t>
+          <t>JOSENI MARIA DE MEDEIROS</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PASSANTE</t>
+          <t>CINTO DO SHORT</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3571,24 +3571,24 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1280</v>
+        <v>1248</v>
       </c>
       <c r="I63" t="n">
-        <v>0.00078125</v>
+        <v>0.01602564102564102</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>PASSANTEPONTO ESTOURADO</t>
+          <t>CINTO DO SHORTPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="L63" t="n">
-        <v>0.75</v>
+        <v>17.6</v>
       </c>
       <c r="M63" t="n">
-        <v>0.8774999999999999</v>
+        <v>20.592</v>
       </c>
       <c r="N63" t="inlineStr"/>
     </row>
@@ -3597,14 +3597,14 @@
         <v>46175</v>
       </c>
       <c r="B64" t="n">
-        <v>300259131</v>
+        <v>300234852</v>
       </c>
       <c r="C64" t="n">
-        <v>16482204</v>
+        <v>15764494</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>POEST INDUSTRIA COMERCIO VESTUARIO LTDA</t>
+          <t>TENDENCIA CONFECCOES LTDA - ME</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -3612,33 +3612,33 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CÓS</t>
+          <t>ETIQUETA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>ESGARÇANDO</t>
+          <t>SEM ARREMATE</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1280</v>
+        <v>1368</v>
       </c>
       <c r="I64" t="n">
-        <v>0.00078125</v>
+        <v>0.0007309941520467836</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>CÓSESGARÇANDO</t>
+          <t>ETIQUETASEM ARREMATE</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>11.13</v>
+        <v>0.33</v>
       </c>
       <c r="L64" t="n">
-        <v>11.13</v>
+        <v>0.33</v>
       </c>
       <c r="M64" t="n">
-        <v>13.0221</v>
+        <v>0.3861</v>
       </c>
       <c r="N64" t="inlineStr"/>
     </row>
@@ -3647,48 +3647,48 @@
         <v>46175</v>
       </c>
       <c r="B65" t="n">
-        <v>300259165</v>
+        <v>300234852</v>
       </c>
       <c r="C65" t="n">
-        <v>16466063</v>
+        <v>15764494</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CONFECÇÕES J.S.LTDA</t>
+          <t>TENDENCIA CONFECCOES LTDA - ME</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ETIQUETA</t>
+          <t>PASSANTE</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SEM ARREMATE</t>
+          <t>PONTO ESTOURADO</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>831</v>
+        <v>1368</v>
       </c>
       <c r="I65" t="n">
-        <v>0.098676293622142</v>
+        <v>0.0007309941520467836</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>ETIQUETASEM ARREMATE</t>
+          <t>PASSANTEPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="L65" t="n">
-        <v>27.06</v>
+        <v>0.75</v>
       </c>
       <c r="M65" t="n">
-        <v>31.6602</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="N65" t="inlineStr"/>
     </row>
@@ -3697,18 +3697,18 @@
         <v>46175</v>
       </c>
       <c r="B66" t="n">
-        <v>300259165</v>
+        <v>300253749</v>
       </c>
       <c r="C66" t="n">
-        <v>16466063</v>
+        <v>16450302</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CONFECÇÕES J.S.LTDA</t>
+          <t>FACCAO ELLO LTDA - ME</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>831</v>
+        <v>1232</v>
       </c>
       <c r="I66" t="n">
-        <v>0.01684717208182912</v>
+        <v>0.008928571428571428</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3735,10 +3735,10 @@
         <v>0.31</v>
       </c>
       <c r="L66" t="n">
-        <v>4.34</v>
+        <v>3.41</v>
       </c>
       <c r="M66" t="n">
-        <v>5.0778</v>
+        <v>3.9897</v>
       </c>
       <c r="N66" t="inlineStr"/>
     </row>
@@ -3758,37 +3758,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ETIQUETA</t>
+          <t>PASSANTE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SEM ARREMATE</t>
+          <t>PONTO ESTOURADO</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>1280</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0078125</v>
+        <v>0.00078125</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>ETIQUETASEM ARREMATE</t>
+          <t>PASSANTEPONTO ESTOURADO</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="L67" t="n">
-        <v>3.3</v>
+        <v>0.75</v>
       </c>
       <c r="M67" t="n">
-        <v>3.861</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="N67" t="inlineStr"/>
     </row>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3817,28 +3817,28 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>PONTO ESTOURADO</t>
+          <t>ESGARÇANDO</t>
         </is>
       </c>
       <c r="H68" t="n">
         <v>1280</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0234375</v>
+        <v>0.00078125</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>CÓSPONTO ESTOURADO</t>
+          <t>CÓSESGARÇANDO</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0.31</v>
+        <v>11.13</v>
       </c>
       <c r="L68" t="n">
-        <v>9.300000000000001</v>
+        <v>11.13</v>
       </c>
       <c r="M68" t="n">
-        <v>10.881</v>
+        <v>13.0221</v>
       </c>
       <c r="N68" t="inlineStr"/>
     </row>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>831</v>
       </c>
       <c r="I69" t="n">
-        <v>0.05054151624548736</v>
+        <v>0.098676293622142</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3885,12 +3885,212 @@
         <v>0.33</v>
       </c>
       <c r="L69" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="M69" t="n">
+        <v>31.6602</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B70" t="n">
+        <v>300259165</v>
+      </c>
+      <c r="C70" t="n">
+        <v>16466063</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CONFECÇÕES J.S.LTDA</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>14</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CÓS</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>831</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.01684717208182912</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>CÓSPONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L70" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="M70" t="n">
+        <v>5.0778</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B71" t="n">
+        <v>300259131</v>
+      </c>
+      <c r="C71" t="n">
+        <v>16482204</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>POEST INDUSTRIA COMERCIO VESTUARIO LTDA</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>10</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ETIQUETA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>1280</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.0078125</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>ETIQUETASEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L71" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M71" t="n">
+        <v>3.861</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B72" t="n">
+        <v>300259131</v>
+      </c>
+      <c r="C72" t="n">
+        <v>16482204</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>POEST INDUSTRIA COMERCIO VESTUARIO LTDA</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>30</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>CÓS</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>PONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1280</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.0234375</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>CÓSPONTO ESTOURADO</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L72" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M72" t="n">
+        <v>10.881</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B73" t="n">
+        <v>300259165</v>
+      </c>
+      <c r="C73" t="n">
+        <v>16466063</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CONFECÇÕES J.S.LTDA</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>42</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ETIQUETA</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>831</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.05054151624548736</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>ETIQUETASEM ARREMATE</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L73" t="n">
         <v>13.86</v>
       </c>
-      <c r="M69" t="n">
+      <c r="M73" t="n">
         <v>16.2162</v>
       </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
